--- a/data/trans_camb/IQ2608_R3-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2608_R3-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>8.667492738389848</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.85483627252614</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.906638748138104</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-25.71494275292968</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>6.854498166981438</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-11.84840681588706</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>2.925314542810703</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.6737378270563</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.438202828896245</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-43.94908207714485</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2.659980431633465</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-23.28443865198474</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>14.05457023706857</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.22419994471592</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.86576004121703</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-8.374349629877004</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>10.72302230506291</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.2679569552706563</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.112930088232403</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.03719609832696932</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.06171779664917774</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3234535267697867</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.08778254881576028</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1517373444951436</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.03635706166900865</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.2376081344399707</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.005807145064910544</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.5556382315135958</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.03377229460356457</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2970211647455027</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.1909407026508328</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1347261811025435</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1409487188310377</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.1083116357894595</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1422511087218157</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.003422957034371205</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>1.695434076604485</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-19.43086263581202</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.04494942000605739</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-16.01430723142885</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.8369219623331592</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-17.61920029790555</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.386261737524231</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-34.57530001388395</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.648251380389632</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-30.68774035118863</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.920389069549119</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-28.00182777614508</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>7.377028631126283</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-4.029559343785474</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.191820937070545</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.0704624875651555</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>5.478750285636311</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-6.611730295146499</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.02015322737797429</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.2309701086308038</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.0005642119573783907</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2010140203785892</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.01022012170436206</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2151578994009541</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.05020208595582509</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4028499032053164</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.08024835249947029</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.3820425541805237</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04564390146862346</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3395011317199821</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.0900993883398878</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.04781283987912523</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.07957506085318909</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.002009790096220975</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.06933520973860581</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.0822379788921357</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-2.48166962281412</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-15.50731868281521</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.842608385430657</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-10.55595780851904</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-3.173277915632433</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-13.33059743413368</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-9.57762891928323</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-26.9412893001859</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-11.44674276793172</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-23.18001203841664</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-8.434224715806224</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-21.13392452139009</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>5.604207957692147</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-5.016849515518497</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.611857796680903</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.8490635699938482</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.160602739189066</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-5.082447921676167</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.03031848132121449</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.189452434564562</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.04704411878764114</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.12923402107385</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.03880824035500412</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1630292218500995</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.115436097957055</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.3197582802904183</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.1345594436224971</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.2757322314634754</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.09994827068651818</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.2580370543494817</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.07115563937769186</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.06129268019059931</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.04558183908690916</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.01039552453531576</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.02742816633233001</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.06426555141919277</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-10.13061945700611</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-14.25812377005209</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-9.698871352912752</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-20.47947208661531</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-9.905295926476631</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-17.2516682895266</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-19.60825545246604</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-30.04310342358426</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-20.82738504775816</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-37.90492272773856</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-16.71751801983297</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-27.74993817104493</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>-1.017822557572504</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.2130620724958331</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.827672248050073</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-7.011365230640136</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-3.464607382325825</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-6.590748557704821</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.1168881791076472</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1645117687073187</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.1142163591140052</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.2411714366752197</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1153599790928471</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.2009179844770604</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.2193446728892861</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3407397482533753</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.236990133566262</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.4311800720341615</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.1892131064586764</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3234793512031862</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>-0.01318212364294858</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.00177110819412164</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.005049807903451401</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.08073498837406505</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-0.04200631691930816</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.07950681513513735</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>1.709589395509103</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-12.84972291672967</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.1215454699587615</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-15.35808887157486</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.8284883365344164</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-13.88641383293292</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-1.702234398928797</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-20.04874817458679</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.896229305974858</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-21.83221574898483</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.317227355002788</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-19.39105876988041</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>5.199625020851037</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-6.055700613130456</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3.07661028460147</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-8.280888604535175</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>3.48239353535517</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-9.198266265923785</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.02100420394451203</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.1578731135572388</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.001506797196990779</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.190393975774464</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.01022362126901622</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.171359607072557</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.02057216551972875</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2441007616205993</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.04709366293424054</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.2680127571531676</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.01624663518826059</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.2395038796908922</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.06473202283692037</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.07592752945709189</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.03906595200405086</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.102740584898594</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.04338052192003255</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.1152526428283958</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
